--- a/outputs/daily/hr_rankings_2026-08-26.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-26.xlsx
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Contact streak: 11/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3735,27 +3735,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>700250</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Ben Rice</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-26T20:07:00Z</t>
+          <t>2026-08-26T23:05:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3798,26 +3798,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>55.6</v>
+        <v>64.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>56.9</v>
+        <v>33</v>
       </c>
       <c r="R13" t="n">
-        <v>28.2</v>
+        <v>38.2</v>
       </c>
       <c r="S13" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>74.2</v>
+        <v>36.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3873,134 +3873,134 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.9% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>50.85</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>90.86</t>
+          <t>92.53</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>103.18</t>
+          <t>102.5716</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4853</t>
+          <t>0.5173</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.2246</t>
+          <t>0.2513</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3426</t>
+          <t>0.3756</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>77.32</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>71.41</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38.28</t>
+          <t>46.29</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1937</t>
+          <t>0.2664</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -4011,27 +4011,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>665833</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oneil Cruz</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-26T20:10:00Z</t>
+          <t>2026-08-26T20:07:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4041,12 +4041,24 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Grayson Rodriguez</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>680570</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
         <v>57.1</v>
       </c>
@@ -4062,26 +4074,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>74.3</v>
+        <v>55.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>56.9</v>
       </c>
       <c r="R14" t="n">
-        <v>22.6</v>
+        <v>28.2</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>48.7</v>
+        <v>74.2</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4095,7 +4107,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4120,7 +4132,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -4137,12 +4149,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -4157,90 +4169,114 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.9% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>57.58</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>95.73</t>
+          <t>90.86</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>107.1754</t>
+          <t>103.18</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4726</t>
+          <t>0.4853</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.2315</t>
+          <t>0.2246</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3471</t>
+          <t>0.3426</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>78.38</t>
+          <t>77.32</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>76.24</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>38.28</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.2088</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+          <t>0.1937</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>46.5</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>90.7</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.477</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>26.2</t>
+        </is>
+      </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -4251,27 +4287,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>700250</t>
+          <t>665833</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ben Rice</t>
+          <t>Oneil Cruz</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-26T23:05:00Z</t>
+          <t>2026-08-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4281,26 +4317,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Peter Lambert</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>663567</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>57</v>
+        <v>57.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4314,26 +4338,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>64.3</v>
+        <v>74.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>33</v>
+        <v>41.2</v>
       </c>
       <c r="R15" t="n">
-        <v>38.2</v>
+        <v>22.6</v>
       </c>
       <c r="S15" t="n">
-        <v>95.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U15" t="n">
-        <v>31.6</v>
+        <v>48.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4347,7 +4371,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4372,7 +4396,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4389,134 +4413,110 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 12.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>57.58</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>92.53</t>
+          <t>95.73</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>102.5716</t>
+          <t>107.1754</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.5173</t>
+          <t>0.4726</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.2513</t>
+          <t>0.2315</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3756</t>
+          <t>0.3471</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>78.38</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>76.24</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>46.29</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.2664</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>6.8</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>36.6</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0.347</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
+          <t>0.2088</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>54.7</v>
+        <v>54.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>89.2</v>
+        <v>93.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -5217,12 +5217,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -7215,27 +7215,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>680664</t>
+          <t>687952</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eduardo Valencia</t>
+          <t>Christian Encarnacion-Strand</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-26T17:10:00Z</t>
+          <t>2026-08-26T23:45:00Z</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Michael McGreevy</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>700241</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -7264,7 +7264,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7282,13 +7282,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>70.40000000000001</v>
+        <v>56.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>35.8</v>
+        <v>53.9</v>
       </c>
       <c r="R26" t="n">
-        <v>27.6</v>
+        <v>22.1</v>
       </c>
       <c r="S26" t="n">
         <v>81.90000000000001</v>
@@ -7297,7 +7297,7 @@
         <v>50</v>
       </c>
       <c r="U26" t="n">
-        <v>27.6</v>
+        <v>51.3</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr"/>
@@ -7353,27 +7353,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.2% barrel, 21.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.6% barrel, 16.2 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -7383,59 +7383,59 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>14.67</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>102.3181</t>
+          <t>101.5339</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.4792</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.3133</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.81</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
+          <t>37.81</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>43.08</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
           <t>30.0</t>
         </is>
       </c>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>36.2</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>27.7</t>
-        </is>
-      </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>6.0</t>
@@ -7443,44 +7443,44 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>0.211</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>41.71</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>87.79</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.3799</t>
+          <t>0.4738</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.1487</t>
+          <t>0.1956</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr"/>
       <c r="BH26" t="inlineStr"/>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -7491,27 +7491,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>695734</t>
+          <t>680664</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>Eduardo Valencia</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-26T22:45:00Z</t>
+          <t>2026-08-26T17:10:00Z</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7521,17 +7521,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Tanner Gordon</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>685299</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -7554,26 +7554,26 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>33</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>62.6</v>
+        <v>35.8</v>
       </c>
       <c r="R27" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S27" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U27" t="n">
-        <v>65.2</v>
+        <v>27.6</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr"/>
@@ -7629,134 +7629,134 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/22, 1 HR</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.5% barrel, 16.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.2% barrel, 21.7 HR allowed</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>37.79</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>88.62</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>98.8173</t>
+          <t>102.3181</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>0.4336</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.1628</t>
+          <t>0.276</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>32.69</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.1752</t>
+          <t>0.364</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>90.94</t>
+          <t>87.79</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>0.4901</t>
+          <t>0.3799</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.1487</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>33.88</t>
+          <t>27.92</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr"/>
       <c r="BH27" t="inlineStr"/>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr"/>
@@ -8043,27 +8043,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>687952</t>
+          <t>695734</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Christian Encarnacion-Strand</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-26T23:45:00Z</t>
+          <t>2026-08-26T22:45:00Z</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8073,17 +8073,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Michael McGreevy</t>
+          <t>Tanner Gordon</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>700241</t>
+          <t>685299</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -8106,26 +8106,26 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>56.6</v>
+        <v>33</v>
       </c>
       <c r="Q29" t="n">
-        <v>53.9</v>
+        <v>62.6</v>
       </c>
       <c r="R29" t="n">
-        <v>22.1</v>
+        <v>28.2</v>
       </c>
       <c r="S29" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T29" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U29" t="n">
-        <v>45.9</v>
+        <v>63.7</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -8201,114 +8201,114 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.6% barrel, 16.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.5% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>14.67</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>37.79</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>88.62</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>101.5339</t>
+          <t>98.8173</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>0.4792</t>
+          <t>0.4336</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1628</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>0.3133</t>
+          <t>0.327</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>73.81</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>41.01</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>32.69</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>0.1752</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>90.94</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>0.4738</t>
+          <t>0.4901</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>0.1956</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>33.88</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr"/>
       <c r="BH29" t="inlineStr"/>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr"/>
@@ -9147,27 +9147,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>695600</t>
+          <t>687263</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-26T23:07:00Z</t>
+          <t>2026-08-26T20:07:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9180,11 +9180,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Joey Cantillo</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>676282</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L33" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9198,26 +9210,26 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>55.2</v>
+        <v>47.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>41.2</v>
+        <v>36.3</v>
       </c>
       <c r="R33" t="n">
-        <v>30.4</v>
+        <v>28.2</v>
       </c>
       <c r="S33" t="n">
         <v>88.7</v>
       </c>
       <c r="T33" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U33" t="n">
-        <v>36</v>
+        <v>81.7</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -9256,7 +9268,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr"/>
@@ -9273,110 +9285,134 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 13.5 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>42.33</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>92.18</t>
+          <t>89.95</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>102.707</t>
+          <t>100.2815</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.4447</t>
+          <t>0.4299</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.3364</t>
+          <t>0.316</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>71.33</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>13.83</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.2031</t>
-        </is>
-      </c>
-      <c r="BA33" t="inlineStr"/>
-      <c r="BB33" t="inlineStr"/>
-      <c r="BC33" t="inlineStr"/>
-      <c r="BD33" t="inlineStr"/>
-      <c r="BE33" t="inlineStr"/>
-      <c r="BF33" t="inlineStr"/>
+          <t>0.203</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>7.69</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>40.33</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>88.52</t>
+        </is>
+      </c>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>0.3672</t>
+        </is>
+      </c>
+      <c r="BE33" t="inlineStr">
+        <is>
+          <t>0.1375</t>
+        </is>
+      </c>
+      <c r="BF33" t="inlineStr">
+        <is>
+          <t>26.88</t>
+        </is>
+      </c>
       <c r="BG33" t="inlineStr"/>
       <c r="BH33" t="inlineStr"/>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr"/>
@@ -9387,27 +9423,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>687263</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Fernando Tatis</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-26T20:07:00Z</t>
+          <t>2026-08-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9422,17 +9458,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Joey Cantillo</t>
+          <t>Bubba Chandler</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>676282</t>
+          <t>696149</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -9450,26 +9486,26 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>47.8</v>
+        <v>56.9</v>
       </c>
       <c r="Q34" t="n">
-        <v>36.3</v>
+        <v>34.2</v>
       </c>
       <c r="R34" t="n">
-        <v>28.2</v>
+        <v>22.6</v>
       </c>
       <c r="S34" t="n">
         <v>88.7</v>
       </c>
       <c r="T34" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U34" t="n">
-        <v>81.7</v>
+        <v>97</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -9525,134 +9561,134 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 4 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 13.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.7% barrel, 8.3 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>42.33</t>
+          <t>53.55</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>89.95</t>
+          <t>93.09</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>100.2815</t>
+          <t>104.4937</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.4299</t>
+          <t>0.4873</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0.1981</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.3742</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>71.33</t>
+          <t>75.58</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>13.83</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>35.15</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>0.1668</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>40.33</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>88.52</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.3672</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1375</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr"/>
       <c r="BH34" t="inlineStr"/>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9663,27 +9699,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>695600</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fernando Tatis</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-26T20:10:00Z</t>
+          <t>2026-08-26T23:07:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9696,21 +9732,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Bubba Chandler</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>696149</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
         <v>52.2</v>
       </c>
@@ -9726,26 +9750,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>56.9</v>
+        <v>55.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>34.2</v>
+        <v>41.2</v>
       </c>
       <c r="R35" t="n">
-        <v>22.6</v>
+        <v>30.4</v>
       </c>
       <c r="S35" t="n">
         <v>88.7</v>
       </c>
       <c r="T35" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U35" t="n">
-        <v>97</v>
+        <v>34.4</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -9784,7 +9808,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr"/>
@@ -9801,134 +9825,110 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Hot streak: 4 HR in last 7 games</t>
+          <t>Last 7 games: 5/22, 1 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.7% barrel, 8.3 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>53.55</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>93.09</t>
+          <t>92.18</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>104.4937</t>
+          <t>102.707</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.4873</t>
+          <t>0.4447</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.1981</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.3742</t>
+          <t>0.3364</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1668</t>
-        </is>
-      </c>
-      <c r="BA35" t="inlineStr">
-        <is>
-          <t>6.74</t>
-        </is>
-      </c>
-      <c r="BB35" t="inlineStr">
-        <is>
-          <t>39.02</t>
-        </is>
-      </c>
-      <c r="BC35" t="inlineStr">
-        <is>
-          <t>89.22</t>
-        </is>
-      </c>
-      <c r="BD35" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="BE35" t="inlineStr">
-        <is>
-          <t>0.149</t>
-        </is>
-      </c>
-      <c r="BF35" t="inlineStr">
-        <is>
-          <t>26.09</t>
-        </is>
-      </c>
+          <t>0.2031</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr"/>
       <c r="BG35" t="inlineStr"/>
       <c r="BH35" t="inlineStr"/>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -12387,27 +12387,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>681715</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Heriberto Hernandez</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-26T23:10:00Z</t>
+          <t>2026-08-26T22:40:00Z</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -12417,17 +12417,17 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Sonny Gray</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>476594</t>
+          <t>543243</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -12436,7 +12436,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -12454,22 +12454,22 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>50.9</v>
+        <v>54.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>50.5</v>
+        <v>37.2</v>
       </c>
       <c r="R45" t="n">
-        <v>24.8</v>
+        <v>21.5</v>
       </c>
       <c r="S45" t="n">
-        <v>88.7</v>
+        <v>95.5</v>
       </c>
       <c r="T45" t="n">
         <v>50</v>
       </c>
       <c r="U45" t="n">
-        <v>28.2</v>
+        <v>60.7</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -12525,134 +12525,134 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.3% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 18.0 HR allowed</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>47.71</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>91.05</t>
+          <t>91.18</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>101.9189</t>
+          <t>101.7587</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>0.4589</t>
+          <t>0.4644</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>0.2042</t>
+          <t>0.2173</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3445</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>74.14</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>45.53</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>28.01</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>0.207</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="BD45" t="inlineStr">
         <is>
-          <t>0.4806</t>
+          <t>0.3845</t>
         </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
-          <t>0.2047</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr"/>
       <c r="BH45" t="inlineStr"/>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr"/>
@@ -12663,27 +12663,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>681715</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Heriberto Hernandez</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-26T22:40:00Z</t>
+          <t>2026-08-26T23:10:00Z</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -12693,17 +12693,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Sonny Gray</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>543243</t>
+          <t>476594</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -12730,22 +12730,22 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>54.2</v>
+        <v>50.9</v>
       </c>
       <c r="Q46" t="n">
-        <v>37.2</v>
+        <v>50.5</v>
       </c>
       <c r="R46" t="n">
-        <v>21.5</v>
+        <v>24.8</v>
       </c>
       <c r="S46" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T46" t="n">
         <v>50</v>
       </c>
       <c r="U46" t="n">
-        <v>60.7</v>
+        <v>26.4</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -12801,134 +12801,134 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 18.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.3% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>47.71</t>
+          <t>45.52</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>91.18</t>
+          <t>91.05</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>101.7587</t>
+          <t>101.9189</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>0.4644</t>
+          <t>0.4589</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>0.2173</t>
+          <t>0.2042</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>0.3445</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>74.14</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>43.61</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>0.186</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>33.97</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>89.19</t>
         </is>
       </c>
       <c r="BD46" t="inlineStr">
         <is>
-          <t>0.3845</t>
+          <t>0.4806</t>
         </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.2047</t>
         </is>
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr"/>
       <c r="BH46" t="inlineStr"/>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr"/>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 2/18, 1 HR</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
@@ -15745,7 +15745,7 @@
         <v>80</v>
       </c>
       <c r="U57" t="n">
-        <v>27.6</v>
+        <v>26.4</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 1 HR</t>
+          <t>Last 7 games: 4/23, 1 HR</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -18816,7 +18816,7 @@
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/26, 0 HR</t>
+          <t>Last 7 games: 3/27, 0 HR</t>
         </is>
       </c>
       <c r="AL68" t="inlineStr">
@@ -22816,7 +22816,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>50</v>
       </c>
       <c r="U83" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -22910,7 +22910,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -22920,7 +22920,7 @@
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 0 HR</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL83" t="inlineStr">
@@ -24217,7 +24217,7 @@
         <v>60</v>
       </c>
       <c r="U88" t="n">
-        <v>46.4</v>
+        <v>45.5</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -26247,27 +26247,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Willi Castro</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-26T23:05:00Z</t>
+          <t>2026-08-26T22:45:00Z</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -26277,26 +26277,14 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Peter Lambert</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>663567</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -26310,26 +26298,26 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>29.8</v>
+        <v>31.7</v>
       </c>
       <c r="Q96" t="n">
-        <v>33</v>
+        <v>40.2</v>
       </c>
       <c r="R96" t="n">
-        <v>38.2</v>
+        <v>28.2</v>
       </c>
       <c r="S96" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T96" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U96" t="n">
-        <v>50.3</v>
+        <v>62.4</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -26343,7 +26331,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
@@ -26368,7 +26356,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD96" t="inlineStr"/>
@@ -26385,7 +26373,7 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI96" t="inlineStr">
@@ -26395,124 +26383,100 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 12.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>39.89</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>98.599</t>
+          <t>100.2352</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>0.4187</t>
+          <t>0.3876</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>0.1505</t>
+          <t>0.1526</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>0.3405</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>72.51</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>26.04</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>42.46</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>31.64</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>0.1737</t>
-        </is>
-      </c>
-      <c r="BA96" t="inlineStr">
-        <is>
-          <t>6.8</t>
-        </is>
-      </c>
-      <c r="BB96" t="inlineStr">
-        <is>
-          <t>36.6</t>
-        </is>
-      </c>
-      <c r="BC96" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
-      </c>
-      <c r="BD96" t="inlineStr">
-        <is>
-          <t>0.347</t>
-        </is>
-      </c>
-      <c r="BE96" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="BF96" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
+          <t>0.1568</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr"/>
+      <c r="BB96" t="inlineStr"/>
+      <c r="BC96" t="inlineStr"/>
+      <c r="BD96" t="inlineStr"/>
+      <c r="BE96" t="inlineStr"/>
+      <c r="BF96" t="inlineStr"/>
       <c r="BG96" t="inlineStr"/>
       <c r="BH96" t="inlineStr"/>
       <c r="BI96" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ96" t="inlineStr"/>
@@ -26523,27 +26487,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>650489</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Willi Castro</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-26T22:45:00Z</t>
+          <t>2026-08-26T23:05:00Z</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -26553,12 +26517,24 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Peter Lambert</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>663567</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L97" t="n">
         <v>45.7</v>
       </c>
@@ -26574,26 +26550,26 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>31.7</v>
+        <v>29.8</v>
       </c>
       <c r="Q97" t="n">
-        <v>40.2</v>
+        <v>33</v>
       </c>
       <c r="R97" t="n">
-        <v>28.2</v>
+        <v>38.2</v>
       </c>
       <c r="S97" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T97" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U97" t="n">
-        <v>62.4</v>
+        <v>48.3</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -26607,7 +26583,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -26632,7 +26608,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr"/>
@@ -26649,110 +26625,134 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>39.89</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>100.2352</t>
+          <t>98.599</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>0.3876</t>
+          <t>0.4187</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>0.1526</t>
+          <t>0.1505</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>0.3081</t>
+          <t>0.3405</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>72.51</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>42.46</t>
+          <t>42.19</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>31.64</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>0.1568</t>
-        </is>
-      </c>
-      <c r="BA97" t="inlineStr"/>
-      <c r="BB97" t="inlineStr"/>
-      <c r="BC97" t="inlineStr"/>
-      <c r="BD97" t="inlineStr"/>
-      <c r="BE97" t="inlineStr"/>
-      <c r="BF97" t="inlineStr"/>
+          <t>0.1737</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>36.6</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>0.347</t>
+        </is>
+      </c>
+      <c r="BE97" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="BF97" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
       <c r="BG97" t="inlineStr"/>
       <c r="BH97" t="inlineStr"/>
       <c r="BI97" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ97" t="inlineStr"/>
@@ -47067,27 +47067,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>664983</t>
+          <t>699393</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Jake McCarthy</t>
+          <t>Pedro Ramirez</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-26T22:45:00Z</t>
+          <t>2026-08-26T19:40:00Z</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -47097,14 +47097,26 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Eduardo Rodriguez</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>593958</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L173" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -47118,26 +47130,26 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P173" t="n">
-        <v>15</v>
+        <v>22.7</v>
       </c>
       <c r="Q173" t="n">
-        <v>41.2</v>
+        <v>38.4</v>
       </c>
       <c r="R173" t="n">
         <v>28.2</v>
       </c>
       <c r="S173" t="n">
-        <v>88.7</v>
+        <v>59.8</v>
       </c>
       <c r="T173" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U173" t="n">
-        <v>24.9</v>
+        <v>37.8</v>
       </c>
       <c r="V173" t="inlineStr">
         <is>
@@ -47151,7 +47163,7 @@
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y173" t="inlineStr">
@@ -47176,7 +47188,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr"/>
@@ -47193,7 +47205,7 @@
       </c>
       <c r="AH173" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI173" t="inlineStr">
@@ -47203,17 +47215,17 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 0 HR</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AL173" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.1% barrel, 17.3 HR allowed</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
@@ -47223,80 +47235,104 @@
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
         <is>
-          <t>96.7515</t>
+          <t>100.0464</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>0.3964</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>0.1322</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr">
         <is>
-          <t>0.3098</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>70.82</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>0.1739</t>
-        </is>
-      </c>
-      <c r="BA173" t="inlineStr"/>
-      <c r="BB173" t="inlineStr"/>
-      <c r="BC173" t="inlineStr"/>
-      <c r="BD173" t="inlineStr"/>
-      <c r="BE173" t="inlineStr"/>
-      <c r="BF173" t="inlineStr"/>
+          <t>0.149</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>8.06</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>34.85</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
+        <is>
+          <t>87.85</t>
+        </is>
+      </c>
+      <c r="BD173" t="inlineStr">
+        <is>
+          <t>0.4345</t>
+        </is>
+      </c>
+      <c r="BE173" t="inlineStr">
+        <is>
+          <t>0.172</t>
+        </is>
+      </c>
+      <c r="BF173" t="inlineStr">
+        <is>
+          <t>27.33</t>
+        </is>
+      </c>
       <c r="BG173" t="inlineStr"/>
       <c r="BH173" t="inlineStr"/>
       <c r="BI173" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ173" t="inlineStr"/>
@@ -47307,27 +47343,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>699393</t>
+          <t>664983</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Pedro Ramirez</t>
+          <t>Jake McCarthy</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-08-26T19:40:00Z</t>
+          <t>2026-08-26T22:45:00Z</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -47337,24 +47373,12 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Eduardo Rodriguez</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>593958</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
       <c r="L174" t="n">
         <v>38</v>
       </c>
@@ -47370,26 +47394,26 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P174" t="n">
-        <v>22.7</v>
+        <v>15</v>
       </c>
       <c r="Q174" t="n">
-        <v>38.4</v>
+        <v>41.2</v>
       </c>
       <c r="R174" t="n">
         <v>28.2</v>
       </c>
       <c r="S174" t="n">
-        <v>59.8</v>
+        <v>88.7</v>
       </c>
       <c r="T174" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="U174" t="n">
-        <v>37.8</v>
+        <v>23.4</v>
       </c>
       <c r="V174" t="inlineStr">
         <is>
@@ -47403,7 +47427,7 @@
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y174" t="inlineStr">
@@ -47428,7 +47452,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD174" t="inlineStr"/>
@@ -47445,27 +47469,27 @@
       </c>
       <c r="AH174" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 1 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL174" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.1% barrel, 17.3 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM174" t="inlineStr">
@@ -47475,104 +47499,80 @@
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>100.0464</t>
+          <t>96.7515</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3964</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.1322</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.3098</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>70.82</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>0.149</t>
-        </is>
-      </c>
-      <c r="BA174" t="inlineStr">
-        <is>
-          <t>8.06</t>
-        </is>
-      </c>
-      <c r="BB174" t="inlineStr">
-        <is>
-          <t>34.85</t>
-        </is>
-      </c>
-      <c r="BC174" t="inlineStr">
-        <is>
-          <t>87.85</t>
-        </is>
-      </c>
-      <c r="BD174" t="inlineStr">
-        <is>
-          <t>0.4345</t>
-        </is>
-      </c>
-      <c r="BE174" t="inlineStr">
-        <is>
-          <t>0.172</t>
-        </is>
-      </c>
-      <c r="BF174" t="inlineStr">
-        <is>
-          <t>27.33</t>
-        </is>
-      </c>
+          <t>0.1739</t>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr"/>
+      <c r="BB174" t="inlineStr"/>
+      <c r="BC174" t="inlineStr"/>
+      <c r="BD174" t="inlineStr"/>
+      <c r="BE174" t="inlineStr"/>
+      <c r="BF174" t="inlineStr"/>
       <c r="BG174" t="inlineStr"/>
       <c r="BH174" t="inlineStr"/>
       <c r="BI174" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ174" t="inlineStr"/>
@@ -60303,27 +60303,27 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>664728</t>
+          <t>701852</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Drew Cavanaugh</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-08-26T23:07:00Z</t>
+          <t>2026-08-26T19:45:00Z</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -60333,14 +60333,26 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Nick Lodolo</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>666157</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L222" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
@@ -60358,22 +60370,22 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>14.1</v>
+        <v>7</v>
       </c>
       <c r="Q222" t="n">
-        <v>41.2</v>
+        <v>48.7</v>
       </c>
       <c r="R222" t="n">
-        <v>30.4</v>
+        <v>19.3</v>
       </c>
       <c r="S222" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T222" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U222" t="n">
-        <v>64.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V222" t="inlineStr">
         <is>
@@ -60387,7 +60399,7 @@
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
@@ -60412,7 +60424,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr"/>
@@ -60429,27 +60441,27 @@
       </c>
       <c r="AH222" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI222" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL222" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM222" t="inlineStr">
@@ -60459,80 +60471,104 @@
       </c>
       <c r="AN222" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>88.64</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>99.2362</t>
+          <t>97.8732</t>
         </is>
       </c>
       <c r="AR222" t="inlineStr">
         <is>
-          <t>0.3187</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>0.0861</t>
+          <t>0.098</t>
         </is>
       </c>
       <c r="AT222" t="inlineStr">
         <is>
-          <t>0.2671</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>71.17</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>0.1197</t>
-        </is>
-      </c>
-      <c r="BA222" t="inlineStr"/>
-      <c r="BB222" t="inlineStr"/>
-      <c r="BC222" t="inlineStr"/>
-      <c r="BD222" t="inlineStr"/>
-      <c r="BE222" t="inlineStr"/>
-      <c r="BF222" t="inlineStr"/>
+          <t>0.012</t>
+        </is>
+      </c>
+      <c r="BA222" t="inlineStr">
+        <is>
+          <t>8.83</t>
+        </is>
+      </c>
+      <c r="BB222" t="inlineStr">
+        <is>
+          <t>40.08</t>
+        </is>
+      </c>
+      <c r="BC222" t="inlineStr">
+        <is>
+          <t>89.99</t>
+        </is>
+      </c>
+      <c r="BD222" t="inlineStr">
+        <is>
+          <t>0.458</t>
+        </is>
+      </c>
+      <c r="BE222" t="inlineStr">
+        <is>
+          <t>0.1778</t>
+        </is>
+      </c>
+      <c r="BF222" t="inlineStr">
+        <is>
+          <t>25.49</t>
+        </is>
+      </c>
       <c r="BG222" t="inlineStr"/>
       <c r="BH222" t="inlineStr"/>
       <c r="BI222" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ222" t="inlineStr"/>
@@ -60543,27 +60579,27 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>701852</t>
+          <t>664728</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Drew Cavanaugh</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-08-26T19:45:00Z</t>
+          <t>2026-08-26T23:07:00Z</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -60573,24 +60609,12 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>Nick Lodolo</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>666157</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
       <c r="L223" t="n">
         <v>33.3</v>
       </c>
@@ -60610,22 +60634,22 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>7</v>
+        <v>14.1</v>
       </c>
       <c r="Q223" t="n">
-        <v>48.7</v>
+        <v>41.2</v>
       </c>
       <c r="R223" t="n">
-        <v>19.3</v>
+        <v>30.4</v>
       </c>
       <c r="S223" t="n">
-        <v>81.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T223" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U223" t="n">
-        <v>9.300000000000001</v>
+        <v>62.4</v>
       </c>
       <c r="V223" t="inlineStr">
         <is>
@@ -60639,7 +60663,7 @@
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y223" t="inlineStr">
@@ -60664,7 +60688,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr"/>
@@ -60681,27 +60705,27 @@
       </c>
       <c r="AH223" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI223" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL223" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 15.7 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM223" t="inlineStr">
@@ -60711,104 +60735,80 @@
       </c>
       <c r="AN223" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>35.26</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.64</t>
         </is>
       </c>
       <c r="AQ223" t="inlineStr">
         <is>
-          <t>97.8732</t>
+          <t>99.2362</t>
         </is>
       </c>
       <c r="AR223" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3187</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>0.0861</t>
         </is>
       </c>
       <c r="AT223" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.2671</t>
         </is>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.17</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>0.012</t>
-        </is>
-      </c>
-      <c r="BA223" t="inlineStr">
-        <is>
-          <t>8.83</t>
-        </is>
-      </c>
-      <c r="BB223" t="inlineStr">
-        <is>
-          <t>40.08</t>
-        </is>
-      </c>
-      <c r="BC223" t="inlineStr">
-        <is>
-          <t>89.99</t>
-        </is>
-      </c>
-      <c r="BD223" t="inlineStr">
-        <is>
-          <t>0.458</t>
-        </is>
-      </c>
-      <c r="BE223" t="inlineStr">
-        <is>
-          <t>0.1778</t>
-        </is>
-      </c>
-      <c r="BF223" t="inlineStr">
-        <is>
-          <t>25.49</t>
-        </is>
-      </c>
+          <t>0.1197</t>
+        </is>
+      </c>
+      <c r="BA223" t="inlineStr"/>
+      <c r="BB223" t="inlineStr"/>
+      <c r="BC223" t="inlineStr"/>
+      <c r="BD223" t="inlineStr"/>
+      <c r="BE223" t="inlineStr"/>
+      <c r="BF223" t="inlineStr"/>
       <c r="BG223" t="inlineStr"/>
       <c r="BH223" t="inlineStr"/>
       <c r="BI223" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ223" t="inlineStr"/>
@@ -61371,27 +61371,27 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>657136</t>
+          <t>702222</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Connor Wong</t>
+          <t>Justin Crawford</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-08-26T22:40:00Z</t>
+          <t>2026-08-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -61401,17 +61401,17 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Ryan Gusto</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>687473</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -61420,7 +61420,7 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="M226" t="inlineStr">
         <is>
@@ -61434,26 +61434,26 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P226" t="n">
-        <v>17.8</v>
+        <v>10.7</v>
       </c>
       <c r="Q226" t="n">
-        <v>48.2</v>
+        <v>42</v>
       </c>
       <c r="R226" t="n">
-        <v>21.5</v>
+        <v>25.4</v>
       </c>
       <c r="S226" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T226" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U226" t="n">
-        <v>39.5</v>
+        <v>26.1</v>
       </c>
       <c r="V226" t="inlineStr">
         <is>
@@ -61467,7 +61467,7 @@
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y226" t="inlineStr">
@@ -61492,7 +61492,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr"/>
@@ -61509,27 +61509,27 @@
       </c>
       <c r="AH226" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI226" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Last 7 games: 5/17, 0 HR</t>
         </is>
       </c>
       <c r="AL226" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.9% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 18.3 HR allowed</t>
         </is>
       </c>
       <c r="AM226" t="inlineStr">
@@ -61539,104 +61539,104 @@
       </c>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>86.55</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>99.2106</t>
+          <t>98.142</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.321</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.063</t>
         </is>
       </c>
       <c r="AT226" t="inlineStr">
         <is>
-          <t>0.2898</t>
+          <t>0.283</t>
         </is>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>72.65</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>0.1089</t>
+          <t>0.088</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>89.59</t>
         </is>
       </c>
       <c r="BD226" t="inlineStr">
         <is>
-          <t>0.4278</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BE226" t="inlineStr">
         <is>
-          <t>0.1683</t>
+          <t>0.1499</t>
         </is>
       </c>
       <c r="BF226" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>28.69</t>
         </is>
       </c>
       <c r="BG226" t="inlineStr"/>
       <c r="BH226" t="inlineStr"/>
       <c r="BI226" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ226" t="inlineStr"/>
@@ -61647,27 +61647,27 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>702222</t>
+          <t>657136</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Justin Crawford</t>
+          <t>Connor Wong</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-08-26T20:10:00Z</t>
+          <t>2026-08-26T22:40:00Z</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -61677,17 +61677,17 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Ryan Gusto</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>687473</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -61710,26 +61710,26 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P227" t="n">
-        <v>10.7</v>
+        <v>17.8</v>
       </c>
       <c r="Q227" t="n">
-        <v>42</v>
+        <v>48.2</v>
       </c>
       <c r="R227" t="n">
-        <v>25.4</v>
+        <v>21.5</v>
       </c>
       <c r="S227" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T227" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U227" t="n">
-        <v>26.1</v>
+        <v>37.8</v>
       </c>
       <c r="V227" t="inlineStr">
         <is>
@@ -61743,7 +61743,7 @@
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y227" t="inlineStr">
@@ -61768,7 +61768,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr"/>
@@ -61785,27 +61785,27 @@
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 18.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.9% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM227" t="inlineStr">
@@ -61815,104 +61815,104 @@
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>35.34</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>86.55</t>
         </is>
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>98.142</t>
+          <t>99.2106</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0.109</t>
         </is>
       </c>
       <c r="AT227" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>0.2898</t>
         </is>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>72.65</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>27.12</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0.1089</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>89.59</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD227" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.4278</t>
         </is>
       </c>
       <c r="BE227" t="inlineStr">
         <is>
-          <t>0.1499</t>
+          <t>0.1683</t>
         </is>
       </c>
       <c r="BF227" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="BG227" t="inlineStr"/>
       <c r="BH227" t="inlineStr"/>
       <c r="BI227" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ227" t="inlineStr"/>
@@ -62751,24 +62751,24 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>691011</t>
+          <t>643376</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Drew Romo</t>
+          <t>Danny Jansen</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
       <c r="F231" t="inlineStr">
         <is>
           <t>2026-08-26T23:40:00Z</t>
@@ -62786,17 +62786,17 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>669022</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L231" t="n">
@@ -62814,14 +62814,14 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P231" t="n">
-        <v>9.9</v>
+        <v>19.6</v>
       </c>
       <c r="Q231" t="n">
-        <v>44.9</v>
+        <v>44.4</v>
       </c>
       <c r="R231" t="n">
         <v>27.6</v>
@@ -62830,10 +62830,10 @@
         <v>40.2</v>
       </c>
       <c r="T231" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U231" t="n">
-        <v>33.7</v>
+        <v>18.3</v>
       </c>
       <c r="V231" t="inlineStr">
         <is>
@@ -62889,12 +62889,12 @@
       </c>
       <c r="AH231" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ231" t="inlineStr">
@@ -62904,112 +62904,112 @@
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 1 HR</t>
+          <t>Last 7 games: 1/14, 1 HR</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.5% barrel, 18.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 18.8 HR allowed</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>87.11</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>95.305</t>
+          <t>97.4711</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>0.2086</t>
+          <t>0.2888</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>0.0777</t>
+          <t>0.1164</t>
         </is>
       </c>
       <c r="AT231" t="inlineStr">
         <is>
-          <t>0.1785</t>
+          <t>0.2598</t>
         </is>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>68.49</t>
+          <t>70.06</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>54.75</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>28.56</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>42.56</t>
+          <t>39.06</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BD231" t="inlineStr">
         <is>
-          <t>0.3877</t>
+          <t>0.3968</t>
         </is>
       </c>
       <c r="BE231" t="inlineStr">
         <is>
-          <t>0.1516</t>
+          <t>0.1634</t>
         </is>
       </c>
       <c r="BF231" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>30.98</t>
         </is>
       </c>
       <c r="BG231" t="inlineStr"/>
@@ -63027,27 +63027,27 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>691011</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Drew Romo</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-08-26T17:10:00Z</t>
+          <t>2026-08-26T23:40:00Z</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -63057,26 +63057,26 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Troy Melton</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>675512</t>
+          <t>669022</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L232" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M232" t="inlineStr">
         <is>
@@ -63090,26 +63090,26 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P232" t="n">
-        <v>12</v>
+        <v>9.9</v>
       </c>
       <c r="Q232" t="n">
-        <v>33.1</v>
+        <v>44.9</v>
       </c>
       <c r="R232" t="n">
         <v>27.6</v>
       </c>
       <c r="S232" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T232" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U232" t="n">
-        <v>32</v>
+        <v>33.7</v>
       </c>
       <c r="V232" t="inlineStr">
         <is>
@@ -63123,7 +63123,7 @@
       </c>
       <c r="X232" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y232" t="inlineStr">
@@ -63165,27 +63165,27 @@
       </c>
       <c r="AH232" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI232" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 4/18, 1 HR</t>
         </is>
       </c>
       <c r="AL232" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 9.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.5% barrel, 18.6 HR allowed</t>
         </is>
       </c>
       <c r="AM232" t="inlineStr">
@@ -63195,104 +63195,104 @@
       </c>
       <c r="AN232" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>85.53</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AQ232" t="inlineStr">
         <is>
-          <t>97.4095</t>
+          <t>95.305</t>
         </is>
       </c>
       <c r="AR232" t="inlineStr">
         <is>
-          <t>0.3493</t>
+          <t>0.2086</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr">
         <is>
-          <t>0.0998</t>
+          <t>0.0777</t>
         </is>
       </c>
       <c r="AT232" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.1785</t>
         </is>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>72.82</t>
+          <t>68.49</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>21.71</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>0.1538</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>42.56</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>89.05</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="BD232" t="inlineStr">
         <is>
-          <t>0.3612</t>
+          <t>0.3877</t>
         </is>
       </c>
       <c r="BE232" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1516</t>
         </is>
       </c>
       <c r="BF232" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="BG232" t="inlineStr"/>
       <c r="BH232" t="inlineStr"/>
       <c r="BI232" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ232" t="inlineStr"/>
@@ -63303,24 +63303,24 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>703601</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Max Clark</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F233" t="inlineStr">
         <is>
           <t>2026-08-26T17:10:00Z</t>
@@ -63333,17 +63333,17 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Troy Melton</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>675512</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -63352,7 +63352,7 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="M233" t="inlineStr">
         <is>
@@ -63366,26 +63366,26 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P233" t="n">
-        <v>15.7</v>
+        <v>12</v>
       </c>
       <c r="Q233" t="n">
-        <v>35.8</v>
+        <v>33.1</v>
       </c>
       <c r="R233" t="n">
         <v>27.6</v>
       </c>
       <c r="S233" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T233" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U233" t="n">
-        <v>27.6</v>
+        <v>32</v>
       </c>
       <c r="V233" t="inlineStr">
         <is>
@@ -63399,7 +63399,7 @@
       </c>
       <c r="X233" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y233" t="inlineStr">
@@ -63424,7 +63424,7 @@
       </c>
       <c r="AC233" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD233" t="inlineStr"/>
@@ -63441,27 +63441,27 @@
       </c>
       <c r="AH233" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI233" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 1 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL233" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 21.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 9.1 HR allowed</t>
         </is>
       </c>
       <c r="AM233" t="inlineStr">
@@ -63471,97 +63471,97 @@
       </c>
       <c r="AN233" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.53</t>
         </is>
       </c>
       <c r="AQ233" t="inlineStr">
         <is>
-          <t>97.3958</t>
+          <t>97.4095</t>
         </is>
       </c>
       <c r="AR233" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.3493</t>
         </is>
       </c>
       <c r="AS233" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.0998</t>
         </is>
       </c>
       <c r="AT233" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.82</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>46.09</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>21.71</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.1538</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>87.79</t>
+          <t>89.05</t>
         </is>
       </c>
       <c r="BD233" t="inlineStr">
         <is>
-          <t>0.3799</t>
+          <t>0.3612</t>
         </is>
       </c>
       <c r="BE233" t="inlineStr">
         <is>
-          <t>0.1487</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BF233" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="BG233" t="inlineStr"/>
@@ -63579,27 +63579,27 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>663968</t>
+          <t>703601</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Max Clark</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2026-08-26T20:10:00Z</t>
+          <t>2026-08-26T17:10:00Z</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -63609,12 +63609,24 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L234" t="n">
         <v>32.1</v>
       </c>
@@ -63634,22 +63646,22 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>6.3</v>
+        <v>15.7</v>
       </c>
       <c r="Q234" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="R234" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="S234" t="n">
         <v>40.2</v>
       </c>
-      <c r="R234" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="S234" t="n">
-        <v>71.7</v>
-      </c>
       <c r="T234" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U234" t="n">
-        <v>4.5</v>
+        <v>27.6</v>
       </c>
       <c r="V234" t="inlineStr">
         <is>
@@ -63663,7 +63675,7 @@
       </c>
       <c r="X234" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y234" t="inlineStr">
@@ -63688,7 +63700,7 @@
       </c>
       <c r="AC234" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD234" t="inlineStr"/>
@@ -63705,27 +63717,27 @@
       </c>
       <c r="AH234" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI234" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 4/22, 1 HR</t>
         </is>
       </c>
       <c r="AL234" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 21.7 HR allowed</t>
         </is>
       </c>
       <c r="AM234" t="inlineStr">
@@ -63735,80 +63747,104 @@
       </c>
       <c r="AN234" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AQ234" t="inlineStr">
         <is>
-          <t>96.7083</t>
+          <t>97.3958</t>
         </is>
       </c>
       <c r="AR234" t="inlineStr">
         <is>
-          <t>0.3325</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr">
         <is>
-          <t>0.0822</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="AT234" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>0.307</t>
         </is>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>67.58</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>0.0846</t>
-        </is>
-      </c>
-      <c r="BA234" t="inlineStr"/>
-      <c r="BB234" t="inlineStr"/>
-      <c r="BC234" t="inlineStr"/>
-      <c r="BD234" t="inlineStr"/>
-      <c r="BE234" t="inlineStr"/>
-      <c r="BF234" t="inlineStr"/>
+          <t>0.122</t>
+        </is>
+      </c>
+      <c r="BA234" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="BB234" t="inlineStr">
+        <is>
+          <t>37.44</t>
+        </is>
+      </c>
+      <c r="BC234" t="inlineStr">
+        <is>
+          <t>87.79</t>
+        </is>
+      </c>
+      <c r="BD234" t="inlineStr">
+        <is>
+          <t>0.3799</t>
+        </is>
+      </c>
+      <c r="BE234" t="inlineStr">
+        <is>
+          <t>0.1487</t>
+        </is>
+      </c>
+      <c r="BF234" t="inlineStr">
+        <is>
+          <t>27.92</t>
+        </is>
+      </c>
       <c r="BG234" t="inlineStr"/>
       <c r="BH234" t="inlineStr"/>
       <c r="BI234" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ234" t="inlineStr"/>
@@ -63819,27 +63855,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>663968</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Jake Mangum</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2026-08-26T17:10:00Z</t>
+          <t>2026-08-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -63849,26 +63885,14 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>Troy Melton</t>
-        </is>
-      </c>
-      <c r="J235" t="inlineStr">
-        <is>
-          <t>675512</t>
-        </is>
-      </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
       <c r="L235" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="M235" t="inlineStr">
         <is>
@@ -63886,22 +63910,22 @@
         </is>
       </c>
       <c r="P235" t="n">
-        <v>0.2</v>
+        <v>6.3</v>
       </c>
       <c r="Q235" t="n">
-        <v>33.1</v>
+        <v>40.2</v>
       </c>
       <c r="R235" t="n">
-        <v>27.6</v>
+        <v>22.6</v>
       </c>
       <c r="S235" t="n">
-        <v>81.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T235" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U235" t="n">
-        <v>22.4</v>
+        <v>4.5</v>
       </c>
       <c r="V235" t="inlineStr">
         <is>
@@ -63915,7 +63939,7 @@
       </c>
       <c r="X235" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y235" t="inlineStr">
@@ -63940,7 +63964,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD235" t="inlineStr"/>
@@ -63957,12 +63981,12 @@
       </c>
       <c r="AH235" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI235" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ235" t="inlineStr">
@@ -63972,12 +63996,12 @@
       </c>
       <c r="AK235" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 3/20, 0 HR</t>
         </is>
       </c>
       <c r="AL235" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 9.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM235" t="inlineStr">
@@ -63987,104 +64011,80 @@
       </c>
       <c r="AN235" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AQ235" t="inlineStr">
         <is>
-          <t>92.869</t>
+          <t>96.7083</t>
         </is>
       </c>
       <c r="AR235" t="inlineStr">
         <is>
-          <t>0.3066</t>
+          <t>0.3325</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0822</t>
         </is>
       </c>
       <c r="AT235" t="inlineStr">
         <is>
-          <t>0.2725</t>
+          <t>0.283</t>
         </is>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>64.66</t>
+          <t>67.58</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>28.34</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>0.0528</t>
-        </is>
-      </c>
-      <c r="BA235" t="inlineStr">
-        <is>
-          <t>6.78</t>
-        </is>
-      </c>
-      <c r="BB235" t="inlineStr">
-        <is>
-          <t>39.75</t>
-        </is>
-      </c>
-      <c r="BC235" t="inlineStr">
-        <is>
-          <t>89.05</t>
-        </is>
-      </c>
-      <c r="BD235" t="inlineStr">
-        <is>
-          <t>0.3612</t>
-        </is>
-      </c>
-      <c r="BE235" t="inlineStr">
-        <is>
-          <t>0.1442</t>
-        </is>
-      </c>
-      <c r="BF235" t="inlineStr">
-        <is>
-          <t>25.26</t>
-        </is>
-      </c>
+          <t>0.0846</t>
+        </is>
+      </c>
+      <c r="BA235" t="inlineStr"/>
+      <c r="BB235" t="inlineStr"/>
+      <c r="BC235" t="inlineStr"/>
+      <c r="BD235" t="inlineStr"/>
+      <c r="BE235" t="inlineStr"/>
+      <c r="BF235" t="inlineStr"/>
       <c r="BG235" t="inlineStr"/>
       <c r="BH235" t="inlineStr"/>
       <c r="BI235" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ235" t="inlineStr"/>
@@ -64095,27 +64095,27 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>683766</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Christian Koss</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2026-08-26T19:45:00Z</t>
+          <t>2026-08-26T17:10:00Z</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -64125,22 +64125,22 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Nick Lodolo</t>
+          <t>Troy Melton</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>666157</t>
+          <t>675512</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L236" t="n">
@@ -64162,22 +64162,22 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>10.8</v>
+        <v>0.2</v>
       </c>
       <c r="Q236" t="n">
-        <v>48.7</v>
+        <v>33.1</v>
       </c>
       <c r="R236" t="n">
-        <v>19.3</v>
+        <v>27.6</v>
       </c>
       <c r="S236" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T236" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U236" t="n">
-        <v>22.9</v>
+        <v>22.4</v>
       </c>
       <c r="V236" t="inlineStr">
         <is>
@@ -64191,7 +64191,7 @@
       </c>
       <c r="X236" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y236" t="inlineStr">
@@ -64233,12 +64233,12 @@
       </c>
       <c r="AH236" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI236" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ236" t="inlineStr">
@@ -64248,12 +64248,12 @@
       </c>
       <c r="AK236" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL236" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 15.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 9.1 HR allowed</t>
         </is>
       </c>
       <c r="AM236" t="inlineStr">
@@ -64263,104 +64263,104 @@
       </c>
       <c r="AN236" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>85.36</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="AQ236" t="inlineStr">
         <is>
-          <t>97.2632</t>
+          <t>92.869</t>
         </is>
       </c>
       <c r="AR236" t="inlineStr">
         <is>
-          <t>0.3131</t>
+          <t>0.3066</t>
         </is>
       </c>
       <c r="AS236" t="inlineStr">
         <is>
-          <t>0.0921</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT236" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>0.2725</t>
         </is>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>64.66</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>28.34</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>0.0648</t>
+          <t>0.0528</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>40.08</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>89.99</t>
+          <t>89.05</t>
         </is>
       </c>
       <c r="BD236" t="inlineStr">
         <is>
-          <t>0.458</t>
+          <t>0.3612</t>
         </is>
       </c>
       <c r="BE236" t="inlineStr">
         <is>
-          <t>0.1778</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BF236" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="BG236" t="inlineStr"/>
       <c r="BH236" t="inlineStr"/>
       <c r="BI236" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ236" t="inlineStr"/>
@@ -64371,27 +64371,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>668952</t>
+          <t>683766</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Ryan Kreidler</t>
+          <t>Christian Koss</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-08-27T01:05:00Z</t>
+          <t>2026-08-26T19:45:00Z</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -64406,21 +64406,21 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>Nick Lodolo</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>666157</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L237" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
@@ -64434,26 +64434,26 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P237" t="n">
-        <v>25.1</v>
+        <v>10.8</v>
       </c>
       <c r="Q237" t="n">
-        <v>30.2</v>
+        <v>48.7</v>
       </c>
       <c r="R237" t="n">
-        <v>30.9</v>
+        <v>19.3</v>
       </c>
       <c r="S237" t="n">
         <v>40.2</v>
       </c>
       <c r="T237" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U237" t="n">
-        <v>30.3</v>
+        <v>22.9</v>
       </c>
       <c r="V237" t="inlineStr">
         <is>
@@ -64509,27 +64509,27 @@
       </c>
       <c r="AH237" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI237" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/5, 1 HR</t>
+          <t>Last 7 games: 6/22, 0 HR</t>
         </is>
       </c>
       <c r="AL237" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.7% barrel, 14.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM237" t="inlineStr">
@@ -64539,104 +64539,104 @@
       </c>
       <c r="AN237" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>85.36</t>
         </is>
       </c>
       <c r="AQ237" t="inlineStr">
         <is>
-          <t>99.1871</t>
+          <t>97.2632</t>
         </is>
       </c>
       <c r="AR237" t="inlineStr">
         <is>
-          <t>0.3376</t>
+          <t>0.3131</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr">
         <is>
-          <t>0.1301</t>
+          <t>0.0921</t>
         </is>
       </c>
       <c r="AT237" t="inlineStr">
         <is>
-          <t>0.2682</t>
+          <t>0.255</t>
         </is>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>32.16</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>28.58</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>0.1085</t>
+          <t>0.0648</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>40.08</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>89.99</t>
         </is>
       </c>
       <c r="BD237" t="inlineStr">
         <is>
-          <t>0.3663</t>
+          <t>0.458</t>
         </is>
       </c>
       <c r="BE237" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.1778</t>
         </is>
       </c>
       <c r="BF237" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BG237" t="inlineStr"/>
       <c r="BH237" t="inlineStr"/>
       <c r="BI237" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ237" t="inlineStr"/>
@@ -64647,27 +64647,27 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>665926</t>
+          <t>668952</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Andres Gimenez</t>
+          <t>Ryan Kreidler</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-08-26T23:07:00Z</t>
+          <t>2026-08-27T01:05:00Z</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -64677,17 +64677,17 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Randy Dobnak</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>677976</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -64696,7 +64696,7 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>31.4</v>
+        <v>31.8</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
@@ -64710,26 +64710,26 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P238" t="n">
-        <v>6.5</v>
+        <v>25.1</v>
       </c>
       <c r="Q238" t="n">
-        <v>31.7</v>
+        <v>30.2</v>
       </c>
       <c r="R238" t="n">
-        <v>30.4</v>
+        <v>30.9</v>
       </c>
       <c r="S238" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T238" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U238" t="n">
-        <v>30</v>
+        <v>30.3</v>
       </c>
       <c r="V238" t="inlineStr">
         <is>
@@ -64743,7 +64743,7 @@
       </c>
       <c r="X238" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y238" t="inlineStr">
@@ -64785,27 +64785,27 @@
       </c>
       <c r="AH238" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 1/5, 1 HR</t>
         </is>
       </c>
       <c r="AL238" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.3% barrel, 1.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.7% barrel, 14.9 HR allowed</t>
         </is>
       </c>
       <c r="AM238" t="inlineStr">
@@ -64815,104 +64815,104 @@
       </c>
       <c r="AN238" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="AQ238" t="inlineStr">
         <is>
-          <t>95.7821</t>
+          <t>99.1871</t>
         </is>
       </c>
       <c r="AR238" t="inlineStr">
         <is>
-          <t>0.3316</t>
+          <t>0.3376</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0.1301</t>
         </is>
       </c>
       <c r="AT238" t="inlineStr">
         <is>
-          <t>0.2786</t>
+          <t>0.2682</t>
         </is>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>68.46</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>32.16</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>28.58</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>0.1121</t>
+          <t>0.1085</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>91.46</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="BD238" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.3663</t>
         </is>
       </c>
       <c r="BE238" t="inlineStr">
         <is>
-          <t>0.1254</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BF238" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BG238" t="inlineStr"/>
       <c r="BH238" t="inlineStr"/>
       <c r="BI238" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ238" t="inlineStr"/>
@@ -64923,27 +64923,27 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>643376</t>
+          <t>665926</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Danny Jansen</t>
+          <t>Andres Gimenez</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-08-26T23:40:00Z</t>
+          <t>2026-08-26T23:07:00Z</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -64953,17 +64953,17 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Randy Dobnak</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>677976</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -64986,26 +64986,26 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P239" t="n">
-        <v>19.6</v>
+        <v>6.5</v>
       </c>
       <c r="Q239" t="n">
-        <v>44.4</v>
+        <v>31.7</v>
       </c>
       <c r="R239" t="n">
-        <v>27.6</v>
+        <v>30.4</v>
       </c>
       <c r="S239" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T239" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U239" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V239" t="inlineStr">
         <is>
@@ -65019,7 +65019,7 @@
       </c>
       <c r="X239" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y239" t="inlineStr">
@@ -65061,134 +65061,134 @@
       </c>
       <c r="AH239" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI239" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ239" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK239" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/13, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL239" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 18.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.3% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN239" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>87.11</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ239" t="inlineStr">
         <is>
-          <t>97.4711</t>
+          <t>95.7821</t>
         </is>
       </c>
       <c r="AR239" t="inlineStr">
         <is>
-          <t>0.2888</t>
+          <t>0.3316</t>
         </is>
       </c>
       <c r="AS239" t="inlineStr">
         <is>
-          <t>0.1164</t>
+          <t>0.095</t>
         </is>
       </c>
       <c r="AT239" t="inlineStr">
         <is>
-          <t>0.2598</t>
+          <t>0.2786</t>
         </is>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>70.06</t>
+          <t>68.46</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>54.75</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>28.56</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.1121</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>39.06</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>91.46</t>
         </is>
       </c>
       <c r="BD239" t="inlineStr">
         <is>
-          <t>0.3968</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="BE239" t="inlineStr">
         <is>
-          <t>0.1634</t>
+          <t>0.1254</t>
         </is>
       </c>
       <c r="BF239" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="BG239" t="inlineStr"/>
       <c r="BH239" t="inlineStr"/>
       <c r="BI239" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ239" t="inlineStr"/>
@@ -69998,7 +69998,7 @@
       </c>
       <c r="AI257" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ257" t="inlineStr">
@@ -70008,7 +70008,7 @@
       </c>
       <c r="AK257" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/16, 0 HR</t>
+          <t>Last 7 games: 0/17, 0 HR</t>
         </is>
       </c>
       <c r="AL257" t="inlineStr">
@@ -73564,7 +73564,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -73574,7 +73574,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Contact streak: 11/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -74801,27 +74801,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>700250</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Ben Rice</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-26T20:07:00Z</t>
+          <t>2026-08-26T23:05:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -74831,17 +74831,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -74850,7 +74850,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -74864,26 +74864,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>55.6</v>
+        <v>64.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>56.9</v>
+        <v>33</v>
       </c>
       <c r="R13" t="n">
-        <v>28.2</v>
+        <v>38.2</v>
       </c>
       <c r="S13" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>74.2</v>
+        <v>36.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -74897,7 +74897,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -74939,134 +74939,134 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.9% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>50.85</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>90.86</t>
+          <t>92.53</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>103.18</t>
+          <t>102.5716</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4853</t>
+          <t>0.5173</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.2246</t>
+          <t>0.2513</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3426</t>
+          <t>0.3756</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>77.32</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>71.41</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38.28</t>
+          <t>46.29</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1937</t>
+          <t>0.2664</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -75077,27 +75077,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>665833</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oneil Cruz</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-26T20:10:00Z</t>
+          <t>2026-08-26T20:07:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -75107,12 +75107,24 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Grayson Rodriguez</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>680570</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
         <v>57.1</v>
       </c>
@@ -75128,26 +75140,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>74.3</v>
+        <v>55.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>56.9</v>
       </c>
       <c r="R14" t="n">
-        <v>22.6</v>
+        <v>28.2</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>48.7</v>
+        <v>74.2</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -75161,7 +75173,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -75186,7 +75198,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -75203,12 +75215,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -75223,90 +75235,114 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.9% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>57.58</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>95.73</t>
+          <t>90.86</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>107.1754</t>
+          <t>103.18</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4726</t>
+          <t>0.4853</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.2315</t>
+          <t>0.2246</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3471</t>
+          <t>0.3426</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>78.38</t>
+          <t>77.32</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>76.24</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>38.28</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.2088</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+          <t>0.1937</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>46.5</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>90.7</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.477</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>26.2</t>
+        </is>
+      </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -75317,27 +75353,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>700250</t>
+          <t>665833</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ben Rice</t>
+          <t>Oneil Cruz</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-26T23:05:00Z</t>
+          <t>2026-08-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -75347,26 +75383,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Peter Lambert</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>663567</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>57</v>
+        <v>57.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -75380,26 +75404,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>64.3</v>
+        <v>74.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>33</v>
+        <v>41.2</v>
       </c>
       <c r="R15" t="n">
-        <v>38.2</v>
+        <v>22.6</v>
       </c>
       <c r="S15" t="n">
-        <v>95.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U15" t="n">
-        <v>31.6</v>
+        <v>48.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -75413,7 +75437,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -75438,7 +75462,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -75455,134 +75479,110 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 12.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>57.58</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>92.53</t>
+          <t>95.73</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>102.5716</t>
+          <t>107.1754</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.5173</t>
+          <t>0.4726</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.2513</t>
+          <t>0.2315</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3756</t>
+          <t>0.3471</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>78.38</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>76.24</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>46.29</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.2664</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>6.8</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>36.6</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0.347</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
+          <t>0.2088</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -76194,7 +76194,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>54.7</v>
+        <v>54.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -76227,7 +76227,7 @@
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>89.2</v>
+        <v>93.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -76283,12 +76283,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
